--- a/docs/Data_Speak_Data_Dictionary.xlsx
+++ b/docs/Data_Speak_Data_Dictionary.xlsx
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2705,28 +2705,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>is_suggested</t>
+          <t>suggestion_reason</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>varchar(300)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>True when system-suggested and not yet edited</t>
+          <t>Why the suggested meaning and aggregation were chosen, from the model or the software baseline; shown at Profile and Define (FEAT-DEF-004)</t>
         </is>
       </c>
     </row>
@@ -2738,22 +2734,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_suggested</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>True when system-suggested and not yet edited</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2763,7 +2767,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2783,29 +2787,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>evidence</t>
+          <t>field_definitions</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2830,7 +2830,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -2842,12 +2846,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>evidence_key</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2857,11 +2861,7 @@
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Deterministic key from FastAPI, e.g. ev_3f9a...</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>analysis_family</t>
+          <t>evidence_key</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2885,14 +2885,10 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>analysis_family</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>enum analysis_family</t>
+          <t>Deterministic key from FastAPI, e.g. ev_3f9a...</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2900,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>metric</t>
+          <t>analysis_family</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>varchar(32)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2918,10 +2914,14 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>analysis_family</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>e.g. monthly_growth_rate</t>
+          <t>enum analysis_family</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>metric</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>e.g. period_over_period_growth</t>
+          <t>e.g. monthly_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2962,24 +2962,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>numeric(24,8)</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Full-precision scalar; null when the result is non-scalar</t>
+          <t>e.g. period_over_period_growth</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>display_value</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>numeric(24,8)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3008,7 +3008,7 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Formatted, e.g. +3.1%</t>
+          <t>Full-precision scalar; null when the result is non-scalar</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>metric_column_id</t>
+          <t>display_value</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3037,7 +3037,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Measure column</t>
+          <t>Formatted, e.g. +3.1%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>dimension_column_id</t>
+          <t>metric_column_id</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3066,7 +3066,7 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Grouping/time column</t>
+          <t>Measure column</t>
         </is>
       </c>
     </row>
@@ -3078,28 +3078,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>source_columns</t>
+          <t>dimension_column_id</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>'[]'</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Array of source column names</t>
+          <t>Grouping/time column</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3107,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>parameters</t>
+          <t>source_columns</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3126,13 +3122,13 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>'{}'</t>
+          <t>'[]'</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Method parameters for reproducibility</t>
+          <t>Array of source column names</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3140,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>quality_status</t>
+          <t>parameters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>varchar(16)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3159,17 +3155,13 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>'ACCEPTABLE'</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>quality_status</t>
-        </is>
-      </c>
+          <t>'{}'</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>enum quality_status</t>
+          <t>Method parameters for reproducibility</t>
         </is>
       </c>
     </row>
@@ -3181,24 +3173,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>quality_status</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar(16)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>'ACCEPTABLE'</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Structured detail: group aggregates, period series, test stats. Aggregates only.</t>
+          <t>enum quality_status</t>
         </is>
       </c>
     </row>
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3225,34 +3225,34 @@
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Structured detail: group aggregates, period series, test stats. Aggregates only.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>insights</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3277,7 +3277,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
     </row>
@@ -3289,7 +3293,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>evidence_id</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3304,11 +3308,7 @@
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Primary supporting evidence</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>insight_type</t>
+          <t>evidence_id</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3332,14 +3332,10 @@
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>insight_type</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>enum insight_type</t>
+          <t>Primary supporting evidence</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3347,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>headline</t>
+          <t>insight_type</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>varchar(32)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3365,10 +3361,14 @@
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>insight_type</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neutral, non-causal wording</t>
+          <t>enum insight_type</t>
         </is>
       </c>
     </row>
@@ -3380,22 +3380,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>headline</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>varchar(1000)</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neutral, non-causal wording</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3405,26 +3409,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>numeric(6,4)</t>
+          <t>varchar(1000)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Ranking score 0-1</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>numeric(6,4)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3451,7 +3451,7 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1 = strongest</t>
+          <t>Ranking score 0-1</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>is_selected</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3476,15 +3476,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Included in report</t>
+          <t>1 = strongest</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3492,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>supporting_evidence_keys</t>
+          <t>is_selected</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3511,13 +3507,13 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>'[]'</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>All evidence keys referenced</t>
+          <t>Included in report</t>
         </is>
       </c>
     </row>
@@ -3529,49 +3525,53 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>supporting_evidence_keys</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>'[]'</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>All evidence keys referenced</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>visualizations</t>
+          <t>insights</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3596,7 +3596,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
     </row>
@@ -3608,7 +3612,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>insight_id</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3618,16 +3622,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Insight the chart illustrates, if any</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3637,28 +3637,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>chart_type</t>
+          <t>insight_id</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>varchar(16)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>chart_type</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>enum chart_type</t>
+          <t>Insight the chart illustrates, if any</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3666,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>chart_type</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3683,15 +3679,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>'RECOMMENDED'</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>chart_type</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>enum visualization_source: recommended by PY-API-006 or added by the user (FEAT-VIS-003)</t>
+          <t>enum chart_type</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3699,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>varchar(16)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3716,9 +3712,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>'RECOMMENDED'</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>enum visualization_source: recommended by PY-API-006 or added by the user (FEAT-VIS-003)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3728,12 +3732,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>spec</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3743,11 +3747,7 @@
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>x/y fields, labels, unit, series (aggregated points)</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>evidence_keys</t>
+          <t>spec</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3770,13 +3770,13 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>'[]'</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>x/y fields, labels, unit, series (aggregated points)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>position</t>
+          <t>evidence_keys</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3801,15 +3801,11 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>'[]'</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Display order</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3819,12 +3815,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>is_selected</t>
+          <t>position</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3834,13 +3830,13 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kept for the report after chart review (FEAT-VIS-003)</t>
+          <t>Display order</t>
         </is>
       </c>
     </row>
@@ -3852,49 +3848,53 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_selected</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Kept for the report after chart review (FEAT-VIS-003)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ai_generations</t>
+          <t>visualizations</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3919,7 +3919,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
     </row>
@@ -3931,12 +3935,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>generation_type</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3945,16 +3949,8 @@
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>ai_generation_type</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>enum ai_generation_type</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3964,12 +3960,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>generation_type</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>varchar(16)</t>
+          <t>varchar(32)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3977,19 +3973,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>'PENDING'</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ai_generation_status</t>
+          <t>ai_generation_type</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>enum ai_generation_status</t>
+          <t>enum ai_generation_type</t>
         </is>
       </c>
     </row>
@@ -4001,12 +3993,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>attempt_no</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>varchar(16)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4016,11 +4008,19 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+          <t>'PENDING'</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ai_generation_status</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>enum ai_generation_status</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4030,26 +4030,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>attempt_no</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>varchar(128)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>e.g. Qwen2.5-7B-Instruct</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>prompt_version</t>
+          <t>model</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>varchar(128)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4074,7 +4074,11 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>e.g. Qwen2.5-7B-Instruct</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4084,12 +4088,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>request_payload</t>
+          <t>prompt_version</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar(32)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4099,11 +4103,7 @@
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Evidence keys and derived values sent to the gateway</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>response_payload</t>
+          <t>request_payload</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4130,7 +4130,7 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Structured output</t>
+          <t>Evidence keys and derived values sent to the gateway</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>response_payload</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4157,7 +4157,11 @@
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Structured output</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4167,7 +4171,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>output_tokens</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4192,7 +4196,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>duration_ms</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4217,12 +4221,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>error_code</t>
+          <t>duration_ms</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4242,12 +4246,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>error_code</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4267,7 +4271,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4287,29 +4291,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>claims</t>
+          <t>ai_generations</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
     </row>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>public_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4334,13 +4334,13 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>External identifier {claimId}</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>public_id</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4365,7 +4365,11 @@
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>External identifier {claimId}</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4375,7 +4379,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ai_generation_id</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4385,16 +4389,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Null for deterministic (non-AI) claims</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4404,28 +4404,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>claim_kind</t>
+          <t>ai_generation_id</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>claim_kind</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>enum claim_kind</t>
+          <t>Null for deterministic (non-AI) claims</t>
         </is>
       </c>
     </row>
@@ -4437,12 +4433,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>claim_kind</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar(32)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4451,10 +4447,14 @@
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>claim_kind</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Narrative sentence</t>
+          <t>enum claim_kind</t>
         </is>
       </c>
     </row>
@@ -4466,24 +4466,24 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>statement_translations</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Verified translations of the statement template per language {locale: template}; placeholders identical to statement (FEAT-I18N-003)</t>
+          <t>Narrative sentence</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>claimed_value</t>
+          <t>statement_translations</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>varchar(128)</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4512,7 +4512,7 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Value as stated in the sentence</t>
+          <t>Verified translations of the statement template per language {locale: template}; placeholders identical to statement (FEAT-I18N-003)</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>computed_value</t>
+          <t>claimed_value</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4541,7 +4541,7 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Value from evidence used to validate</t>
+          <t>Value as stated in the sentence</t>
         </is>
       </c>
     </row>
@@ -4553,32 +4553,24 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>computed_value</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>varchar(16)</t>
+          <t>varchar(128)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>'PENDING'</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>claim_status</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>enum claim_status</t>
+          <t>Value from evidence used to validate</t>
         </is>
       </c>
     </row>
@@ -4590,24 +4582,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>validation_method</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>varchar(16)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>'PENDING'</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>claim_status</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>e.g. numeric_tolerance, nli</t>
+          <t>enum claim_status</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>validation_notes</t>
+          <t>validation_method</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>varchar(500)</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4634,7 +4634,11 @@
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>e.g. numeric_tolerance, nli</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4644,30 +4648,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>in_report</t>
+          <t>validation_notes</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>varchar(500)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Only SUPPORTED claims may be true</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4677,24 +4673,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>position</t>
+          <t>in_report</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Order within report section</t>
+          <t>Only SUPPORTED claims may be true</t>
         </is>
       </c>
     </row>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>position</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4721,7 +4721,11 @@
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Order within report section</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4731,7 +4735,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4751,22 +4755,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>claim_evidence</t>
+          <t>claims</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>claim_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4781,7 +4785,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>evidence_id</t>
+          <t>claim_id</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4806,12 +4810,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>is_primary</t>
+          <t>evidence_id</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4819,17 +4823,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Exactly one primary per claim (application rule)</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4839,49 +4835,53 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_primary</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Exactly one primary per claim (application rule)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>reports</t>
+          <t>claim_evidence</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>analysis_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4906,13 +4906,13 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>1:1 with analyses</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>analysis_id</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>varchar(16)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4935,19 +4935,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>'DRAFT'</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>report_status</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>enum report_status</t>
+          <t>1:1 with analyses</t>
         </is>
       </c>
     </row>
@@ -4959,12 +4951,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>varchar(8)</t>
+          <t>varchar(16)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4974,13 +4966,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>'en'</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
+          <t>'DRAFT'</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>report_status</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Language of the narrative, labels and PDF (en, th, zh, my) (FEAT-I18N-003)</t>
+          <t>enum report_status</t>
         </is>
       </c>
     </row>
@@ -4992,12 +4988,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>varchar(8)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5005,9 +5001,17 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>'en'</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Language of the narrative, labels and PDF (en, th, zh, my) (FEAT-I18N-003)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5017,17 +5021,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>generated_at</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5042,24 +5046,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>claims_total</t>
+          <t>generated_at</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>claims_supported</t>
+          <t>claims_total</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>summary_metrics</t>
+          <t>claims_supported</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>KPI cards: evidence_key, label, display_value, unit</t>
-        </is>
-      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>sections</t>
+          <t>summary_metrics</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5146,7 +5146,7 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Narrative sections referencing claim public_ids</t>
+          <t>KPI cards: evidence_key, label, display_value, unit</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>data_notes</t>
+          <t>sections</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5175,7 +5175,7 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Warnings / insufficient-data notes</t>
+          <t>Narrative sections referencing claim public_ids</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>data_notes</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5202,7 +5202,11 @@
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Warnings / insufficient-data notes</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5212,7 +5216,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5232,29 +5236,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>personal_access_tokens</t>
+          <t>reports</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>tokenable_type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5279,13 +5279,13 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Polymorphic</t>
-        </is>
-      </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>tokenable_id</t>
+          <t>tokenable_type</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5310,7 +5310,11 @@
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Polymorphic</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5320,12 +5324,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>tokenable_id</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5345,12 +5349,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>varchar(64)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5360,11 +5364,7 @@
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Hashed</t>
-        </is>
-      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5374,22 +5374,26 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>abilities</t>
+          <t>token</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar(64)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Hashed</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5399,12 +5403,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>last_used_at</t>
+          <t>abilities</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5424,7 +5428,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>last_used_at</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5449,7 +5453,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5474,7 +5478,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5490,6 +5494,31 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>personal_access_tokens</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
